--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run8/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run8/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8345,0.1663,0.0183,0.0179</t>
-  </si>
-  <si>
-    <t>0.0488,0.0028,0.0019,0.9823</t>
-  </si>
-  <si>
-    <t>0.4665,0.0847,0.0366,0.4503</t>
-  </si>
-  <si>
-    <t>0.0525,0.0089,0.1664,0.8872</t>
-  </si>
-  <si>
-    <t>0.9941,0.0041,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9836,0.0248,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.9829,0.0148,0.0019,0.0017</t>
-  </si>
-  <si>
-    <t>0.9904,0.0078,0.0015,0.0010</t>
-  </si>
-  <si>
-    <t>0.9814,0.0182,0.0031,0.0012</t>
-  </si>
-  <si>
-    <t>0.9861,0.0090,0.0013,0.0026</t>
-  </si>
-  <si>
-    <t>0.9861,0.0159,0.0016,0.0008</t>
-  </si>
-  <si>
-    <t>0.9908,0.0072,0.0010,0.0010</t>
-  </si>
-  <si>
-    <t>0.6153,0.1547,0.2056,0.0485</t>
-  </si>
-  <si>
-    <t>0.0866,0.8375,0.1394,0.0060</t>
-  </si>
-  <si>
-    <t>0.3895,0.1939,0.5040,0.0171</t>
-  </si>
-  <si>
-    <t>0.0674,0.0585,0.9047,0.0051</t>
-  </si>
-  <si>
-    <t>0.2359,0.7186,0.0660,0.0362</t>
-  </si>
-  <si>
-    <t>0.0099,0.9823,0.0293,0.0002</t>
-  </si>
-  <si>
-    <t>0.0035,0.9916,0.0054,0.0004</t>
-  </si>
-  <si>
-    <t>0.1630,0.8838,0.0143,0.0006</t>
-  </si>
-  <si>
-    <t>0.0160,0.9773,0.0195,0.0003</t>
-  </si>
-  <si>
-    <t>0.0185,0.9613,0.0545,0.0003</t>
-  </si>
-  <si>
-    <t>0.1114,0.0725,0.1174,0.8390</t>
-  </si>
-  <si>
-    <t>0.1855,0.2154,0.6126,0.0556</t>
-  </si>
-  <si>
-    <t>0.0811,0.1471,0.7865,0.0452</t>
-  </si>
-  <si>
-    <t>0.2013,0.1948,0.6165,0.0575</t>
-  </si>
-  <si>
-    <t>0.0799,0.0655,0.8563,0.0503</t>
-  </si>
-  <si>
-    <t>0.0558,0.0248,0.9063,0.0608</t>
-  </si>
-  <si>
-    <t>0.0020,0.0052,0.9801,0.0444</t>
-  </si>
-  <si>
-    <t>0.7453,0.4323,0.0052,0.0015</t>
-  </si>
-  <si>
-    <t>0.2842,0.1529,0.6560,0.0061</t>
-  </si>
-  <si>
-    <t>0.0001,0.0044,0.9945,0.0205</t>
-  </si>
-  <si>
-    <t>0.0535,0.7617,0.2634,0.0007</t>
-  </si>
-  <si>
-    <t>0.8507,0.1331,0.0139,0.0218</t>
-  </si>
-  <si>
-    <t>0.1855,0.6334,0.1641,0.0019</t>
-  </si>
-  <si>
-    <t>0.5578,0.5621,0.0274,0.0047</t>
-  </si>
-  <si>
-    <t>0.0415,0.9093,0.2273,0.0038</t>
-  </si>
-  <si>
-    <t>0.0024,0.9234,0.3559,0.0175</t>
-  </si>
-  <si>
-    <t>0.0156,0.7019,0.7318,0.0149</t>
-  </si>
-  <si>
-    <t>0.0094,0.4126,0.5328,0.1563</t>
-  </si>
-  <si>
-    <t>0.0766,0.0574,0.7048,0.2493</t>
-  </si>
-  <si>
-    <t>0.0224,0.2639,0.8291,0.0353</t>
-  </si>
-  <si>
-    <t>0.0112,0.9215,0.3082,0.0105</t>
-  </si>
-  <si>
-    <t>0.0425,0.5104,0.7104,0.0203</t>
-  </si>
-  <si>
-    <t>0.1598,0.6583,0.1055,0.3872</t>
-  </si>
-  <si>
-    <t>0.0017,0.9843,0.0328,0.0138</t>
-  </si>
-  <si>
-    <t>0.0007,0.9925,0.0296,0.0022</t>
-  </si>
-  <si>
-    <t>0.0001,0.9983,0.0249,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.2567,0.9340,0.0123</t>
-  </si>
-  <si>
-    <t>0.0051,0.1393,0.9284,0.0263</t>
-  </si>
-  <si>
-    <t>0.0984,0.1615,0.5371,0.3352</t>
-  </si>
-  <si>
-    <t>0.0400,0.0054,0.9500,0.0314</t>
-  </si>
-  <si>
-    <t>0.0297,0.0793,0.8904,0.0687</t>
-  </si>
-  <si>
-    <t>0.0207,0.2533,0.8658,0.0107</t>
-  </si>
-  <si>
-    <t>0.9766,0.0259,0.0029,0.0013</t>
-  </si>
-  <si>
-    <t>0.9536,0.0248,0.0204,0.0044</t>
-  </si>
-  <si>
-    <t>0.9559,0.0276,0.0107,0.0059</t>
-  </si>
-  <si>
-    <t>0.0100,0.1739,0.9619,0.0028</t>
-  </si>
-  <si>
-    <t>0.9770,0.0190,0.0043,0.0016</t>
-  </si>
-  <si>
-    <t>0.9943,0.0026,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.9743,0.0219,0.0057,0.0019</t>
-  </si>
-  <si>
-    <t>0.0012,0.8446,0.8916,0.0016</t>
-  </si>
-  <si>
-    <t>0.0001,0.0332,0.9931,0.0027</t>
-  </si>
-  <si>
-    <t>0.0028,0.3690,0.9439,0.0066</t>
-  </si>
-  <si>
-    <t>0.0014,0.8382,0.9319,0.0003</t>
-  </si>
-  <si>
-    <t>0.0020,0.1237,0.9780,0.0039</t>
-  </si>
-  <si>
-    <t>0.0195,0.8997,0.1183,0.0004</t>
-  </si>
-  <si>
-    <t>0.0004,0.9971,0.0060,0.0002</t>
-  </si>
-  <si>
-    <t>0.3092,0.3328,0.3820,0.0040</t>
-  </si>
-  <si>
-    <t>0.2392,0.6548,0.1695,0.0043</t>
-  </si>
-  <si>
-    <t>0.0454,0.1421,0.9005,0.0145</t>
-  </si>
-  <si>
-    <t>0.0021,0.9328,0.6226,0.0028</t>
-  </si>
-  <si>
-    <t>0.0045,0.9057,0.7115,0.0038</t>
-  </si>
-  <si>
-    <t>0.0002,0.9892,0.0849,0.0043</t>
-  </si>
-  <si>
-    <t>0.0049,0.8698,0.6936,0.0040</t>
-  </si>
-  <si>
-    <t>0.0014,0.0037,0.0015,0.9981</t>
-  </si>
-  <si>
-    <t>0.0061,0.0030,0.0004,0.9970</t>
-  </si>
-  <si>
-    <t>0.0054,0.0456,0.0031,0.9914</t>
-  </si>
-  <si>
-    <t>0.0274,0.0143,0.0035,0.9835</t>
-  </si>
-  <si>
-    <t>0.0569,0.0090,0.0319,0.9525</t>
-  </si>
-  <si>
-    <t>0.0026,0.0134,0.0013,0.9968</t>
-  </si>
-  <si>
-    <t>0.0015,0.9382,0.6767,0.0017</t>
-  </si>
-  <si>
-    <t>0.0009,0.5805,0.9402,0.0032</t>
-  </si>
-  <si>
-    <t>0.0061,0.7151,0.7205,0.0010</t>
-  </si>
-  <si>
-    <t>0.0037,0.5299,0.9376,0.0014</t>
-  </si>
-  <si>
-    <t>0.0028,0.7876,0.8844,0.0008</t>
-  </si>
-  <si>
-    <t>0.0024,0.9429,0.6596,0.0010</t>
-  </si>
-  <si>
-    <t>0.9924,0.0035,0.0003,0.0021</t>
-  </si>
-  <si>
-    <t>0.9922,0.0060,0.0011,0.0007</t>
-  </si>
-  <si>
-    <t>0.9748,0.0220,0.0042,0.0014</t>
-  </si>
-  <si>
-    <t>0.9902,0.0054,0.0007,0.0021</t>
-  </si>
-  <si>
-    <t>0.9888,0.0050,0.0015,0.0022</t>
-  </si>
-  <si>
-    <t>0.9919,0.0050,0.0007,0.0015</t>
-  </si>
-  <si>
-    <t>0.9726,0.0442,0.0024,0.0008</t>
-  </si>
-  <si>
-    <t>0.9922,0.0038,0.0006,0.0017</t>
-  </si>
-  <si>
-    <t>0.9945,0.0016,0.0002,0.0022</t>
-  </si>
-  <si>
-    <t>0.9933,0.0044,0.0006,0.0009</t>
-  </si>
-  <si>
-    <t>0.9926,0.0032,0.0005,0.0018</t>
-  </si>
-  <si>
-    <t>0.9931,0.0046,0.0008,0.0008</t>
-  </si>
-  <si>
-    <t>0.9892,0.0047,0.0009,0.0028</t>
-  </si>
-  <si>
-    <t>0.9928,0.0049,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9941,0.0037,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.9929,0.0043,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.0069,0.0208,0.9444,0.0783</t>
-  </si>
-  <si>
-    <t>0.1778,0.4465,0.4412,0.1242</t>
-  </si>
-  <si>
-    <t>0.1094,0.0308,0.2619,0.7341</t>
-  </si>
-  <si>
-    <t>0.0756,0.0403,0.9032,0.0133</t>
-  </si>
-  <si>
-    <t>0.0159,0.9741,0.0149,0.0009</t>
-  </si>
-  <si>
-    <t>0.0169,0.9743,0.0200,0.0003</t>
-  </si>
-  <si>
-    <t>0.0389,0.9582,0.0233,0.0007</t>
-  </si>
-  <si>
-    <t>0.0565,0.9583,0.0056,0.0003</t>
-  </si>
-  <si>
-    <t>0.0074,0.9888,0.0067,0.0002</t>
-  </si>
-  <si>
-    <t>0.0050,0.9899,0.0046,0.0002</t>
-  </si>
-  <si>
-    <t>0.1862,0.8488,0.0140,0.0007</t>
-  </si>
-  <si>
-    <t>0.4768,0.1678,0.4192,0.0954</t>
-  </si>
-  <si>
-    <t>0.2845,0.1034,0.6621,0.0320</t>
-  </si>
-  <si>
-    <t>0.3054,0.3458,0.0809,0.3822</t>
-  </si>
-  <si>
-    <t>0.4315,0.1210,0.4429,0.0904</t>
-  </si>
-  <si>
-    <t>0.0652,0.1979,0.0148,0.9039</t>
-  </si>
-  <si>
-    <t>0.0002,0.9980,0.0247,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.9933,0.0284,0.0018</t>
-  </si>
-  <si>
-    <t>0.0069,0.9689,0.0099,0.0216</t>
-  </si>
-  <si>
-    <t>0.0002,0.9916,0.2986,0.0004</t>
-  </si>
-  <si>
-    <t>0.0114,0.9779,0.0714,0.0007</t>
-  </si>
-  <si>
-    <t>0.8261,0.1458,0.0634,0.0105</t>
-  </si>
-  <si>
-    <t>0.0532,0.9414,0.0478,0.0006</t>
-  </si>
-  <si>
-    <t>0.9727,0.0333,0.0038,0.0017</t>
-  </si>
-  <si>
-    <t>0.9823,0.0066,0.0013,0.0066</t>
-  </si>
-  <si>
-    <t>0.9781,0.0243,0.0015,0.0019</t>
-  </si>
-  <si>
-    <t>0.9565,0.0346,0.0153,0.0026</t>
-  </si>
-  <si>
-    <t>0.9938,0.0015,0.0003,0.0025</t>
-  </si>
-  <si>
-    <t>0.9676,0.0305,0.0037,0.0030</t>
-  </si>
-  <si>
-    <t>0.9825,0.0101,0.0011,0.0039</t>
-  </si>
-  <si>
-    <t>0.9946,0.0012,0.0003,0.0021</t>
-  </si>
-  <si>
-    <t>0.0060,0.7493,0.8500,0.0024</t>
-  </si>
-  <si>
-    <t>0.0050,0.8719,0.6415,0.0014</t>
-  </si>
-  <si>
-    <t>0.0357,0.6394,0.7113,0.0171</t>
-  </si>
-  <si>
-    <t>0.0231,0.7208,0.5451,0.0271</t>
-  </si>
-  <si>
-    <t>0.0940,0.0628,0.2392,0.7860</t>
-  </si>
-  <si>
-    <t>0.4623,0.4224,0.1421,0.0347</t>
-  </si>
-  <si>
-    <t>0.2713,0.0915,0.7369,0.0052</t>
-  </si>
-  <si>
-    <t>0.3734,0.5362,0.1670,0.0127</t>
-  </si>
-  <si>
-    <t>0.0642,0.0349,0.0383,0.9385</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0046,0.0052,0.0034,0.9953</t>
-  </si>
-  <si>
-    <t>0.0065,0.0060,0.0098,0.9913</t>
-  </si>
-  <si>
-    <t>0.0017,0.8415,0.9029,0.0010</t>
-  </si>
-  <si>
-    <t>0.9756,0.0042,0.0006,0.0148</t>
-  </si>
-  <si>
-    <t>0.8663,0.1578,0.0180,0.0078</t>
-  </si>
-  <si>
-    <t>0.9727,0.0080,0.0009,0.0133</t>
-  </si>
-  <si>
-    <t>0.9145,0.1292,0.0085,0.0018</t>
-  </si>
-  <si>
-    <t>0.9687,0.0087,0.0073,0.0077</t>
-  </si>
-  <si>
-    <t>0.5954,0.2762,0.1841,0.0291</t>
-  </si>
-  <si>
-    <t>0.9733,0.0150,0.0051,0.0050</t>
-  </si>
-  <si>
-    <t>0.0005,0.1211,0.9861,0.0028</t>
-  </si>
-  <si>
-    <t>0.9155,0.0130,0.0145,0.0271</t>
-  </si>
-  <si>
-    <t>0.9259,0.0256,0.0243,0.0169</t>
-  </si>
-  <si>
-    <t>0.1419,0.7442,0.1598,0.0057</t>
-  </si>
-  <si>
-    <t>0.7882,0.1535,0.0906,0.0082</t>
-  </si>
-  <si>
-    <t>0.5986,0.4588,0.0336,0.0082</t>
-  </si>
-  <si>
-    <t>0.2434,0.6699,0.1357,0.0867</t>
-  </si>
-  <si>
-    <t>0.4038,0.5492,0.0936,0.0026</t>
-  </si>
-  <si>
-    <t>0.4651,0.5805,0.0660,0.0068</t>
-  </si>
-  <si>
-    <t>0.9813,0.0112,0.0035,0.0023</t>
-  </si>
-  <si>
-    <t>0.9755,0.0183,0.0045,0.0029</t>
-  </si>
-  <si>
-    <t>0.9910,0.0038,0.0005,0.0024</t>
-  </si>
-  <si>
-    <t>0.9737,0.0107,0.0033,0.0080</t>
-  </si>
-  <si>
-    <t>0.9671,0.0158,0.0069,0.0062</t>
-  </si>
-  <si>
-    <t>0.9821,0.0159,0.0032,0.0013</t>
-  </si>
-  <si>
-    <t>0.9865,0.0037,0.0010,0.0050</t>
-  </si>
-  <si>
-    <t>0.9862,0.0101,0.0009,0.0020</t>
-  </si>
-  <si>
-    <t>0.4897,0.5847,0.0415,0.0021</t>
-  </si>
-  <si>
-    <t>0.5556,0.5718,0.0174,0.0012</t>
-  </si>
-  <si>
-    <t>0.6259,0.5036,0.0214,0.0014</t>
-  </si>
-  <si>
-    <t>0.0664,0.8368,0.2075,0.0006</t>
-  </si>
-  <si>
-    <t>0.9733,0.0262,0.0019,0.0034</t>
-  </si>
-  <si>
-    <t>0.8961,0.1211,0.0219,0.0037</t>
-  </si>
-  <si>
-    <t>0.9857,0.0108,0.0028,0.0014</t>
-  </si>
-  <si>
-    <t>0.7933,0.3025,0.0161,0.0016</t>
-  </si>
-  <si>
-    <t>0.0028,0.0102,0.9954,0.0030</t>
-  </si>
-  <si>
-    <t>0.9399,0.0532,0.0133,0.0036</t>
-  </si>
-  <si>
-    <t>0.0036,0.0121,0.9852,0.0150</t>
-  </si>
-  <si>
-    <t>0.0136,0.0389,0.9689,0.0087</t>
-  </si>
-  <si>
-    <t>0.1106,0.3498,0.5317,0.0070</t>
-  </si>
-  <si>
-    <t>0.0033,0.1763,0.9193,0.0212</t>
-  </si>
-  <si>
-    <t>0.0688,0.0302,0.9239,0.0046</t>
-  </si>
-  <si>
-    <t>0.0307,0.0171,0.9496,0.0204</t>
-  </si>
-  <si>
-    <t>0.0035,0.0014,0.9944,0.0059</t>
-  </si>
-  <si>
-    <t>0.1009,0.6537,0.3613,0.0121</t>
-  </si>
-  <si>
-    <t>0.0453,0.0077,0.9654,0.0095</t>
-  </si>
-  <si>
-    <t>0.2257,0.7746,0.0615,0.0148</t>
-  </si>
-  <si>
-    <t>0.0490,0.5010,0.6034,0.0028</t>
-  </si>
-  <si>
-    <t>0.0353,0.8981,0.1427,0.0020</t>
-  </si>
-  <si>
-    <t>0.4116,0.4073,0.1857,0.0801</t>
-  </si>
-  <si>
-    <t>0.4566,0.1875,0.4060,0.0495</t>
-  </si>
-  <si>
-    <t>0.0381,0.9092,0.1087,0.0029</t>
-  </si>
-  <si>
-    <t>0.9251,0.0770,0.0133,0.0057</t>
-  </si>
-  <si>
-    <t>0.9606,0.0694,0.0038,0.0007</t>
-  </si>
-  <si>
-    <t>0.8879,0.2215,0.0056,0.0007</t>
-  </si>
-  <si>
-    <t>0.9693,0.0274,0.0038,0.0029</t>
-  </si>
-  <si>
-    <t>0.9850,0.0152,0.0013,0.0013</t>
-  </si>
-  <si>
-    <t>0.2758,0.6247,0.1724,0.0559</t>
-  </si>
-  <si>
-    <t>0.6012,0.1859,0.2415,0.0467</t>
-  </si>
-  <si>
-    <t>0.2728,0.2875,0.2774,0.3536</t>
-  </si>
-  <si>
-    <t>0.1775,0.1477,0.6958,0.0196</t>
-  </si>
-  <si>
-    <t>0.4415,0.0821,0.2214,0.2795</t>
-  </si>
-  <si>
-    <t>0.0130,0.0330,0.9692,0.0047</t>
-  </si>
-  <si>
-    <t>0.0221,0.6759,0.5382,0.0649</t>
-  </si>
-  <si>
-    <t>0.0140,0.1685,0.9147,0.0157</t>
-  </si>
-  <si>
-    <t>0.0198,0.1110,0.9056,0.0302</t>
-  </si>
-  <si>
-    <t>0.0073,0.2135,0.9199,0.0150</t>
-  </si>
-  <si>
-    <t>0.9884,0.0041,0.0009,0.0037</t>
-  </si>
-  <si>
-    <t>0.9793,0.0309,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.9842,0.0109,0.0014,0.0030</t>
-  </si>
-  <si>
-    <t>0.9617,0.0492,0.0055,0.0017</t>
-  </si>
-  <si>
-    <t>0.9805,0.0165,0.0023,0.0018</t>
-  </si>
-  <si>
-    <t>0.9925,0.0037,0.0010,0.0010</t>
-  </si>
-  <si>
-    <t>0.9835,0.0138,0.0035,0.0011</t>
-  </si>
-  <si>
-    <t>0.9883,0.0126,0.0004,0.0013</t>
-  </si>
-  <si>
-    <t>0.2366,0.2815,0.5171,0.0104</t>
-  </si>
-  <si>
-    <t>0.2441,0.6180,0.1597,0.0032</t>
-  </si>
-  <si>
-    <t>0.6906,0.1108,0.1132,0.0907</t>
-  </si>
-  <si>
-    <t>0.0104,0.1010,0.9409,0.0098</t>
-  </si>
-  <si>
-    <t>0.0014,0.2155,0.9763,0.0018</t>
-  </si>
-  <si>
-    <t>0.0868,0.2583,0.6734,0.0135</t>
-  </si>
-  <si>
-    <t>0.0027,0.0136,0.9742,0.0321</t>
-  </si>
-  <si>
-    <t>0.0373,0.0474,0.9309,0.0152</t>
-  </si>
-  <si>
-    <t>0.0007,0.0596,0.9892,0.0023</t>
-  </si>
-  <si>
-    <t>0.0017,0.0492,0.9500,0.0315</t>
-  </si>
-  <si>
-    <t>0.1603,0.1379,0.7388,0.0164</t>
-  </si>
-  <si>
-    <t>0.3748,0.1784,0.5028,0.0908</t>
-  </si>
-  <si>
-    <t>0.5302,0.1391,0.3420,0.0606</t>
-  </si>
-  <si>
-    <t>0.5586,0.0439,0.4078,0.0532</t>
-  </si>
-  <si>
-    <t>0.9779,0.0230,0.0031,0.0012</t>
-  </si>
-  <si>
-    <t>0.9946,0.0025,0.0003,0.0013</t>
-  </si>
-  <si>
-    <t>0.9913,0.0064,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9853,0.0124,0.0019,0.0013</t>
-  </si>
-  <si>
-    <t>0.9872,0.0055,0.0013,0.0032</t>
-  </si>
-  <si>
-    <t>0.9926,0.0053,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.9946,0.0029,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.9920,0.0010,0.0002,0.0053</t>
-  </si>
-  <si>
-    <t>0.0643,0.4135,0.6272,0.0218</t>
-  </si>
-  <si>
-    <t>0.0008,0.0335,0.9940,0.0015</t>
-  </si>
-  <si>
-    <t>0.0586,0.2025,0.7796,0.0582</t>
-  </si>
-  <si>
-    <t>0.0936,0.1152,0.8086,0.0257</t>
-  </si>
-  <si>
-    <t>0.0303,0.0593,0.9237,0.0253</t>
-  </si>
-  <si>
-    <t>0.0323,0.0221,0.8530,0.1872</t>
-  </si>
-  <si>
-    <t>0.1269,0.4222,0.3940,0.0120</t>
-  </si>
-  <si>
-    <t>0.0199,0.5538,0.5811,0.0834</t>
-  </si>
-  <si>
-    <t>0.7310,0.0053,0.0074,0.3187</t>
-  </si>
-  <si>
-    <t>0.0273,0.0200,0.0036,0.9832</t>
-  </si>
-  <si>
-    <t>0.0479,0.0158,0.0165,0.9659</t>
-  </si>
-  <si>
-    <t>0.0010,0.0015,0.0007,0.9989</t>
-  </si>
-  <si>
-    <t>0.0064,0.0018,0.0012,0.9965</t>
-  </si>
-  <si>
-    <t>0.5424,0.1760,0.1429,0.1873</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.6244,0.3761,0.0296,0.0354</t>
+  </si>
+  <si>
+    <t>0.0043,0.0030,0.0007,0.9972</t>
+  </si>
+  <si>
+    <t>0.8052,0.0577,0.0275,0.1119</t>
+  </si>
+  <si>
+    <t>0.0515,0.0149,0.0035,0.9740</t>
+  </si>
+  <si>
+    <t>0.9936,0.0040,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9856,0.0088,0.0018,0.0027</t>
+  </si>
+  <si>
+    <t>0.9917,0.0042,0.0006,0.0016</t>
+  </si>
+  <si>
+    <t>0.9931,0.0055,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9932,0.0022,0.0005,0.0018</t>
+  </si>
+  <si>
+    <t>0.9908,0.0081,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.9963,0.0022,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9894,0.0103,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.4945,0.3004,0.2291,0.0289</t>
+  </si>
+  <si>
+    <t>0.3823,0.0474,0.6612,0.0295</t>
+  </si>
+  <si>
+    <t>0.1254,0.0985,0.8147,0.0068</t>
+  </si>
+  <si>
+    <t>0.1902,0.1544,0.6561,0.0277</t>
+  </si>
+  <si>
+    <t>0.5281,0.2683,0.2765,0.0109</t>
+  </si>
+  <si>
+    <t>0.0031,0.9927,0.0081,0.0003</t>
+  </si>
+  <si>
+    <t>0.0074,0.9869,0.0103,0.0003</t>
+  </si>
+  <si>
+    <t>0.5437,0.4816,0.0509,0.0035</t>
+  </si>
+  <si>
+    <t>0.0481,0.9542,0.0144,0.0007</t>
+  </si>
+  <si>
+    <t>0.0036,0.9936,0.0050,0.0001</t>
+  </si>
+  <si>
+    <t>0.1728,0.0441,0.7552,0.0808</t>
+  </si>
+  <si>
+    <t>0.1858,0.1273,0.2186,0.6382</t>
+  </si>
+  <si>
+    <t>0.0132,0.1121,0.9307,0.0130</t>
+  </si>
+  <si>
+    <t>0.3608,0.0688,0.6293,0.0282</t>
+  </si>
+  <si>
+    <t>0.1566,0.1738,0.6175,0.0073</t>
+  </si>
+  <si>
+    <t>0.1102,0.1058,0.7904,0.0142</t>
+  </si>
+  <si>
+    <t>0.0036,0.0081,0.9481,0.1198</t>
+  </si>
+  <si>
+    <t>0.4278,0.6318,0.0264,0.0046</t>
+  </si>
+  <si>
+    <t>0.6428,0.1585,0.2923,0.0261</t>
+  </si>
+  <si>
+    <t>0.0006,0.0095,0.9956,0.0045</t>
+  </si>
+  <si>
+    <t>0.0048,0.9789,0.0642,0.0001</t>
+  </si>
+  <si>
+    <t>0.7087,0.2637,0.0422,0.0678</t>
+  </si>
+  <si>
+    <t>0.2369,0.5640,0.1888,0.0053</t>
+  </si>
+  <si>
+    <t>0.8572,0.2349,0.0127,0.0016</t>
+  </si>
+  <si>
+    <t>0.1441,0.8144,0.1239,0.0030</t>
+  </si>
+  <si>
+    <t>0.0023,0.9185,0.2602,0.0311</t>
+  </si>
+  <si>
+    <t>0.0130,0.3406,0.8256,0.0402</t>
+  </si>
+  <si>
+    <t>0.0080,0.8200,0.7130,0.0055</t>
+  </si>
+  <si>
+    <t>0.1391,0.0330,0.5738,0.3005</t>
+  </si>
+  <si>
+    <t>0.0088,0.5316,0.8937,0.0051</t>
+  </si>
+  <si>
+    <t>0.0028,0.9630,0.1636,0.0104</t>
+  </si>
+  <si>
+    <t>0.0156,0.1348,0.8978,0.0453</t>
+  </si>
+  <si>
+    <t>0.0182,0.7440,0.0124,0.7406</t>
+  </si>
+  <si>
+    <t>0.0004,0.9957,0.0282,0.0008</t>
+  </si>
+  <si>
+    <t>0.0018,0.9820,0.1948,0.0011</t>
+  </si>
+  <si>
+    <t>0.0001,0.9972,0.0162,0.0019</t>
+  </si>
+  <si>
+    <t>0.0000,0.0378,0.9906,0.0035</t>
+  </si>
+  <si>
+    <t>0.0012,0.2885,0.9844,0.0006</t>
+  </si>
+  <si>
+    <t>0.0327,0.0907,0.9091,0.0195</t>
+  </si>
+  <si>
+    <t>0.0226,0.0090,0.9498,0.0568</t>
+  </si>
+  <si>
+    <t>0.0335,0.3721,0.7859,0.0359</t>
+  </si>
+  <si>
+    <t>0.0106,0.1491,0.9441,0.0025</t>
+  </si>
+  <si>
+    <t>0.7120,0.4202,0.0104,0.0025</t>
+  </si>
+  <si>
+    <t>0.9735,0.0143,0.0077,0.0027</t>
+  </si>
+  <si>
+    <t>0.9542,0.0418,0.0081,0.0041</t>
+  </si>
+  <si>
+    <t>0.1139,0.0660,0.9031,0.0101</t>
+  </si>
+  <si>
+    <t>0.9887,0.0056,0.0013,0.0025</t>
+  </si>
+  <si>
+    <t>0.9922,0.0046,0.0010,0.0011</t>
+  </si>
+  <si>
+    <t>0.9739,0.0191,0.0030,0.0051</t>
+  </si>
+  <si>
+    <t>0.0022,0.6401,0.9351,0.0022</t>
+  </si>
+  <si>
+    <t>0.0023,0.1519,0.9542,0.0098</t>
+  </si>
+  <si>
+    <t>0.0010,0.0278,0.9698,0.0259</t>
+  </si>
+  <si>
+    <t>0.0013,0.9177,0.8269,0.0011</t>
+  </si>
+  <si>
+    <t>0.0010,0.0184,0.9864,0.0120</t>
+  </si>
+  <si>
+    <t>0.0122,0.9577,0.0863,0.0009</t>
+  </si>
+  <si>
+    <t>0.0003,0.9978,0.0044,0.0002</t>
+  </si>
+  <si>
+    <t>0.3386,0.3854,0.3164,0.0049</t>
+  </si>
+  <si>
+    <t>0.3064,0.2643,0.5066,0.0085</t>
+  </si>
+  <si>
+    <t>0.0170,0.0241,0.9772,0.0101</t>
+  </si>
+  <si>
+    <t>0.0017,0.9324,0.7697,0.0007</t>
+  </si>
+  <si>
+    <t>0.0024,0.8152,0.8994,0.0007</t>
+  </si>
+  <si>
+    <t>0.0003,0.9889,0.1443,0.0008</t>
+  </si>
+  <si>
+    <t>0.0015,0.9182,0.8105,0.0009</t>
+  </si>
+  <si>
+    <t>0.0097,0.0141,0.1047,0.9592</t>
+  </si>
+  <si>
+    <t>0.0014,0.0060,0.0003,0.9986</t>
+  </si>
+  <si>
+    <t>0.0144,0.0107,0.0031,0.9907</t>
+  </si>
+  <si>
+    <t>0.0277,0.0356,0.0193,0.9701</t>
+  </si>
+  <si>
+    <t>0.0065,0.0108,0.0048,0.9932</t>
+  </si>
+  <si>
+    <t>0.0048,0.0072,0.0032,0.9950</t>
+  </si>
+  <si>
+    <t>0.0010,0.9578,0.5881,0.0009</t>
+  </si>
+  <si>
+    <t>0.0011,0.8098,0.9102,0.0017</t>
+  </si>
+  <si>
+    <t>0.0126,0.7295,0.7777,0.0091</t>
+  </si>
+  <si>
+    <t>0.0066,0.5070,0.9017,0.0070</t>
+  </si>
+  <si>
+    <t>0.0006,0.9555,0.7825,0.0003</t>
+  </si>
+  <si>
+    <t>0.0013,0.9462,0.5630,0.0027</t>
+  </si>
+  <si>
+    <t>0.9870,0.0080,0.0012,0.0029</t>
+  </si>
+  <si>
+    <t>0.9895,0.0085,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.9715,0.0247,0.0044,0.0025</t>
+  </si>
+  <si>
+    <t>0.9915,0.0041,0.0005,0.0020</t>
+  </si>
+  <si>
+    <t>0.9893,0.0050,0.0018,0.0017</t>
+  </si>
+  <si>
+    <t>0.9917,0.0057,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.9785,0.0105,0.0054,0.0036</t>
+  </si>
+  <si>
+    <t>0.9914,0.0093,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9865,0.0063,0.0019,0.0028</t>
+  </si>
+  <si>
+    <t>0.9938,0.0040,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9936,0.0041,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.9876,0.0045,0.0016,0.0031</t>
+  </si>
+  <si>
+    <t>0.9910,0.0053,0.0007,0.0017</t>
+  </si>
+  <si>
+    <t>0.9920,0.0053,0.0006,0.0017</t>
+  </si>
+  <si>
+    <t>0.9890,0.0098,0.0011,0.0012</t>
+  </si>
+  <si>
+    <t>0.9940,0.0013,0.0003,0.0023</t>
+  </si>
+  <si>
+    <t>0.0002,0.0073,0.9967,0.0034</t>
+  </si>
+  <si>
+    <t>0.1612,0.2369,0.6195,0.0398</t>
+  </si>
+  <si>
+    <t>0.0635,0.1167,0.0381,0.9205</t>
+  </si>
+  <si>
+    <t>0.0713,0.1508,0.8065,0.0056</t>
+  </si>
+  <si>
+    <t>0.0179,0.9756,0.0107,0.0007</t>
+  </si>
+  <si>
+    <t>0.0048,0.9897,0.0156,0.0002</t>
+  </si>
+  <si>
+    <t>0.1091,0.9232,0.0048,0.0020</t>
+  </si>
+  <si>
+    <t>0.0665,0.9437,0.0097,0.0004</t>
+  </si>
+  <si>
+    <t>0.0040,0.9909,0.0122,0.0003</t>
+  </si>
+  <si>
+    <t>0.0076,0.9873,0.0037,0.0004</t>
+  </si>
+  <si>
+    <t>0.6979,0.4177,0.0154,0.0006</t>
+  </si>
+  <si>
+    <t>0.3574,0.4912,0.0633,0.1617</t>
+  </si>
+  <si>
+    <t>0.3609,0.0877,0.5723,0.0396</t>
+  </si>
+  <si>
+    <t>0.1794,0.4227,0.4415,0.0189</t>
+  </si>
+  <si>
+    <t>0.4517,0.2748,0.2024,0.1426</t>
+  </si>
+  <si>
+    <t>0.2960,0.3058,0.0738,0.4359</t>
+  </si>
+  <si>
+    <t>0.0024,0.9890,0.0668,0.0011</t>
+  </si>
+  <si>
+    <t>0.0003,0.9960,0.0742,0.0004</t>
+  </si>
+  <si>
+    <t>0.1086,0.8227,0.0529,0.0693</t>
+  </si>
+  <si>
+    <t>0.0002,0.9925,0.3076,0.0002</t>
+  </si>
+  <si>
+    <t>0.0159,0.9725,0.0715,0.0006</t>
+  </si>
+  <si>
+    <t>0.1539,0.8843,0.0221,0.0006</t>
+  </si>
+  <si>
+    <t>0.5591,0.5226,0.0555,0.0034</t>
+  </si>
+  <si>
+    <t>0.9737,0.0153,0.0043,0.0032</t>
+  </si>
+  <si>
+    <t>0.9871,0.0054,0.0016,0.0032</t>
+  </si>
+  <si>
+    <t>0.9882,0.0020,0.0005,0.0064</t>
+  </si>
+  <si>
+    <t>0.9874,0.0051,0.0023,0.0018</t>
+  </si>
+  <si>
+    <t>0.9917,0.0030,0.0005,0.0024</t>
+  </si>
+  <si>
+    <t>0.9802,0.0157,0.0034,0.0017</t>
+  </si>
+  <si>
+    <t>0.9860,0.0065,0.0016,0.0031</t>
+  </si>
+  <si>
+    <t>0.9868,0.0018,0.0006,0.0078</t>
+  </si>
+  <si>
+    <t>0.0008,0.9446,0.6988,0.0007</t>
+  </si>
+  <si>
+    <t>0.0097,0.5036,0.8977,0.0047</t>
+  </si>
+  <si>
+    <t>0.0209,0.6702,0.6818,0.0052</t>
+  </si>
+  <si>
+    <t>0.0092,0.7740,0.6800,0.0092</t>
+  </si>
+  <si>
+    <t>0.3158,0.2654,0.2582,0.4668</t>
+  </si>
+  <si>
+    <t>0.5624,0.2132,0.2797,0.0351</t>
+  </si>
+  <si>
+    <t>0.3283,0.0372,0.7763,0.0202</t>
+  </si>
+  <si>
+    <t>0.5399,0.1977,0.2236,0.1312</t>
+  </si>
+  <si>
+    <t>0.0597,0.0174,0.0231,0.9545</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.0002,0.9998</t>
+  </si>
+  <si>
+    <t>0.0029,0.0110,0.0006,0.9973</t>
+  </si>
+  <si>
+    <t>0.0233,0.0043,0.0046,0.9870</t>
+  </si>
+  <si>
+    <t>0.0008,0.9243,0.7338,0.0023</t>
+  </si>
+  <si>
+    <t>0.9578,0.0241,0.0037,0.0115</t>
+  </si>
+  <si>
+    <t>0.4637,0.6902,0.0043,0.0051</t>
+  </si>
+  <si>
+    <t>0.9706,0.0085,0.0006,0.0156</t>
+  </si>
+  <si>
+    <t>0.8456,0.2101,0.0211,0.0016</t>
+  </si>
+  <si>
+    <t>0.9782,0.0158,0.0021,0.0038</t>
+  </si>
+  <si>
+    <t>0.6992,0.1046,0.2773,0.0267</t>
+  </si>
+  <si>
+    <t>0.9748,0.0100,0.0029,0.0073</t>
+  </si>
+  <si>
+    <t>0.0001,0.2350,0.9945,0.0003</t>
+  </si>
+  <si>
+    <t>0.5320,0.0072,0.0203,0.5551</t>
+  </si>
+  <si>
+    <t>0.8998,0.0308,0.0142,0.0512</t>
+  </si>
+  <si>
+    <t>0.1031,0.8854,0.0353,0.0100</t>
+  </si>
+  <si>
+    <t>0.8311,0.2092,0.0262,0.0037</t>
+  </si>
+  <si>
+    <t>0.8871,0.0812,0.0354,0.0081</t>
+  </si>
+  <si>
+    <t>0.1596,0.7430,0.1673,0.0105</t>
+  </si>
+  <si>
+    <t>0.2494,0.6610,0.1593,0.0133</t>
+  </si>
+  <si>
+    <t>0.5067,0.5214,0.0363,0.0259</t>
+  </si>
+  <si>
+    <t>0.9930,0.0033,0.0005,0.0014</t>
+  </si>
+  <si>
+    <t>0.9291,0.0752,0.0132,0.0041</t>
+  </si>
+  <si>
+    <t>0.9906,0.0060,0.0005,0.0019</t>
+  </si>
+  <si>
+    <t>0.9606,0.0251,0.0146,0.0026</t>
+  </si>
+  <si>
+    <t>0.9820,0.0099,0.0027,0.0030</t>
+  </si>
+  <si>
+    <t>0.9845,0.0126,0.0010,0.0019</t>
+  </si>
+  <si>
+    <t>0.9853,0.0092,0.0019,0.0026</t>
+  </si>
+  <si>
+    <t>0.9857,0.0088,0.0007,0.0036</t>
+  </si>
+  <si>
+    <t>0.1883,0.8283,0.0555,0.0029</t>
+  </si>
+  <si>
+    <t>0.4939,0.5816,0.0339,0.0017</t>
+  </si>
+  <si>
+    <t>0.3257,0.7675,0.0096,0.0012</t>
+  </si>
+  <si>
+    <t>0.3153,0.6069,0.1303,0.0015</t>
+  </si>
+  <si>
+    <t>0.9592,0.0674,0.0036,0.0011</t>
+  </si>
+  <si>
+    <t>0.9604,0.0417,0.0078,0.0023</t>
+  </si>
+  <si>
+    <t>0.9743,0.0209,0.0033,0.0037</t>
+  </si>
+  <si>
+    <t>0.8199,0.2165,0.0288,0.0091</t>
+  </si>
+  <si>
+    <t>0.0211,0.8099,0.2148,0.0002</t>
+  </si>
+  <si>
+    <t>0.9420,0.0869,0.0067,0.0010</t>
+  </si>
+  <si>
+    <t>0.0060,0.0479,0.9767,0.0058</t>
+  </si>
+  <si>
+    <t>0.0050,0.1493,0.9685,0.0036</t>
+  </si>
+  <si>
+    <t>0.2155,0.0130,0.8379,0.0259</t>
+  </si>
+  <si>
+    <t>0.0001,0.1581,0.9926,0.0006</t>
+  </si>
+  <si>
+    <t>0.0408,0.0584,0.9261,0.0111</t>
+  </si>
+  <si>
+    <t>0.0120,0.0074,0.9735,0.0260</t>
+  </si>
+  <si>
+    <t>0.0032,0.0206,0.9864,0.0076</t>
+  </si>
+  <si>
+    <t>0.0792,0.6673,0.3258,0.0032</t>
+  </si>
+  <si>
+    <t>0.1961,0.0593,0.7956,0.0160</t>
+  </si>
+  <si>
+    <t>0.3041,0.4265,0.3240,0.0172</t>
+  </si>
+  <si>
+    <t>0.0629,0.4795,0.4358,0.0007</t>
+  </si>
+  <si>
+    <t>0.0624,0.7609,0.2836,0.0100</t>
+  </si>
+  <si>
+    <t>0.3921,0.1933,0.4229,0.0162</t>
+  </si>
+  <si>
+    <t>0.4237,0.3460,0.2869,0.0481</t>
+  </si>
+  <si>
+    <t>0.0616,0.7546,0.2679,0.0024</t>
+  </si>
+  <si>
+    <t>0.7834,0.2955,0.0216,0.0019</t>
+  </si>
+  <si>
+    <t>0.9512,0.0806,0.0028,0.0015</t>
+  </si>
+  <si>
+    <t>0.5590,0.5050,0.0265,0.0008</t>
+  </si>
+  <si>
+    <t>0.9828,0.0223,0.0009,0.0014</t>
+  </si>
+  <si>
+    <t>0.9502,0.0614,0.0100,0.0015</t>
+  </si>
+  <si>
+    <t>0.3038,0.6377,0.1193,0.0315</t>
+  </si>
+  <si>
+    <t>0.4177,0.0846,0.5893,0.0352</t>
+  </si>
+  <si>
+    <t>0.1953,0.6196,0.1150,0.2715</t>
+  </si>
+  <si>
+    <t>0.4548,0.3709,0.1380,0.1062</t>
+  </si>
+  <si>
+    <t>0.4526,0.0405,0.2598,0.2356</t>
+  </si>
+  <si>
+    <t>0.0899,0.1350,0.7959,0.0533</t>
+  </si>
+  <si>
+    <t>0.0140,0.1174,0.6112,0.3049</t>
+  </si>
+  <si>
+    <t>0.0577,0.4093,0.6887,0.0482</t>
+  </si>
+  <si>
+    <t>0.0085,0.4613,0.8514,0.0120</t>
+  </si>
+  <si>
+    <t>0.0070,0.0884,0.8817,0.0795</t>
+  </si>
+  <si>
+    <t>0.9912,0.0025,0.0004,0.0034</t>
+  </si>
+  <si>
+    <t>0.9899,0.0060,0.0010,0.0016</t>
+  </si>
+  <si>
+    <t>0.9825,0.0155,0.0019,0.0017</t>
+  </si>
+  <si>
+    <t>0.9908,0.0079,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9670,0.0469,0.0045,0.0011</t>
+  </si>
+  <si>
+    <t>0.9921,0.0053,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.9900,0.0060,0.0011,0.0017</t>
+  </si>
+  <si>
+    <t>0.9860,0.0101,0.0017,0.0018</t>
+  </si>
+  <si>
+    <t>0.1275,0.0473,0.8913,0.0041</t>
+  </si>
+  <si>
+    <t>0.3002,0.2841,0.5224,0.0131</t>
+  </si>
+  <si>
+    <t>0.8557,0.0161,0.0141,0.1171</t>
+  </si>
+  <si>
+    <t>0.0240,0.0872,0.9316,0.0081</t>
+  </si>
+  <si>
+    <t>0.0155,0.0864,0.9018,0.0507</t>
+  </si>
+  <si>
+    <t>0.0906,0.1063,0.7891,0.0277</t>
+  </si>
+  <si>
+    <t>0.0026,0.0149,0.9809,0.0208</t>
+  </si>
+  <si>
+    <t>0.2234,0.2210,0.5539,0.0435</t>
+  </si>
+  <si>
+    <t>0.0017,0.1591,0.9609,0.0094</t>
+  </si>
+  <si>
+    <t>0.0108,0.1808,0.9388,0.0064</t>
+  </si>
+  <si>
+    <t>0.2535,0.5674,0.2307,0.0433</t>
+  </si>
+  <si>
+    <t>0.5043,0.1739,0.3205,0.0863</t>
+  </si>
+  <si>
+    <t>0.4761,0.0636,0.5199,0.0351</t>
+  </si>
+  <si>
+    <t>0.4521,0.1062,0.2989,0.2418</t>
+  </si>
+  <si>
+    <t>0.9920,0.0059,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9949,0.0028,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9893,0.0060,0.0014,0.0015</t>
+  </si>
+  <si>
+    <t>0.9761,0.0149,0.0020,0.0042</t>
+  </si>
+  <si>
+    <t>0.9849,0.0057,0.0010,0.0047</t>
+  </si>
+  <si>
+    <t>0.9948,0.0033,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9867,0.0102,0.0017,0.0013</t>
+  </si>
+  <si>
+    <t>0.9793,0.0106,0.0058,0.0029</t>
+  </si>
+  <si>
+    <t>0.0364,0.7138,0.4602,0.0188</t>
+  </si>
+  <si>
+    <t>0.0034,0.6566,0.8862,0.0023</t>
+  </si>
+  <si>
+    <t>0.0050,0.0331,0.9805,0.0054</t>
+  </si>
+  <si>
+    <t>0.1783,0.1633,0.6610,0.0348</t>
+  </si>
+  <si>
+    <t>0.0082,0.0220,0.9698,0.0195</t>
+  </si>
+  <si>
+    <t>0.0561,0.0045,0.6987,0.3276</t>
+  </si>
+  <si>
+    <t>0.0853,0.3778,0.6405,0.0252</t>
+  </si>
+  <si>
+    <t>0.0359,0.1938,0.7466,0.0922</t>
+  </si>
+  <si>
+    <t>0.8476,0.0211,0.0128,0.1079</t>
+  </si>
+  <si>
+    <t>0.0278,0.0217,0.0021,0.9836</t>
+  </si>
+  <si>
+    <t>0.0312,0.0074,0.0024,0.9854</t>
+  </si>
+  <si>
+    <t>0.0020,0.0019,0.0013,0.9981</t>
+  </si>
+  <si>
+    <t>0.0012,0.0012,0.0011,0.9987</t>
+  </si>
+  <si>
+    <t>0.6859,0.0665,0.0625,0.1528</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2133,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2147,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2189,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2231,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2444,7 @@
         <v>262</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2486,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2497,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2511,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2539,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,10 +2567,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2917,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2931,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3130,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3144,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,10 +3421,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3438,7 @@
         <v>260</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3561,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3617,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3676,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3701,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3872,7 @@
         <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3886,7 @@
         <v>263</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,10 +3897,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3939,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,10 +4135,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4208,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4222,7 @@
         <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,10 +4233,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4362,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4376,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4390,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4404,7 @@
         <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,10 +4471,10 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4600,7 @@
         <v>262</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4656,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4698,7 @@
         <v>262</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4737,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4782,7 @@
         <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,10 +4793,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4807,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4863,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5171,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5185,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,10 +5213,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5339,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,10 +5353,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5412,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5423,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5437,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
